--- a/myCBD/myInfo/Age Group Standard and US Standard 2000 Population.xlsx
+++ b/myCBD/myInfo/Age Group Standard and US Standard 2000 Population.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0.CBD\myCBD\myInfo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="120" yWindow="135" windowWidth="24915" windowHeight="12090" activeTab="4"/>
+    <workbookView xWindow="120" yWindow="135" windowWidth="24915" windowHeight="12090"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -13,12 +18,12 @@
     <sheet name="teenAge" sheetId="3" r:id="rId4"/>
     <sheet name="drinkAge" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>https://www.cdc.gov/nchs/data/statnt/statnt20.pdf</t>
   </si>
@@ -39,12 +44,45 @@
   </si>
   <si>
     <t>US2000POP</t>
+  </si>
+  <si>
+    <t>ageLabel</t>
+  </si>
+  <si>
+    <t>15 - 24</t>
+  </si>
+  <si>
+    <t>25 - 34</t>
+  </si>
+  <si>
+    <t>35 - 44</t>
+  </si>
+  <si>
+    <t>45 - 54</t>
+  </si>
+  <si>
+    <t>55 - 64</t>
+  </si>
+  <si>
+    <t>65 - 74</t>
+  </si>
+  <si>
+    <t>75 - 84</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0 - 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5 - 14</t>
+  </si>
+  <si>
+    <t>85+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -83,12 +121,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -99,6 +139,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -147,7 +190,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -182,7 +225,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -391,13 +434,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="52.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -407,8 +450,11 @@
       <c r="C1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -418,8 +464,11 @@
       <c r="C2">
         <v>18987</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5</v>
       </c>
@@ -429,8 +478,11 @@
       <c r="C3">
         <v>39977</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>15</v>
       </c>
@@ -440,8 +492,11 @@
       <c r="C4">
         <v>38077</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25</v>
       </c>
@@ -451,8 +506,11 @@
       <c r="C5">
         <v>37233</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>35</v>
       </c>
@@ -462,8 +520,11 @@
       <c r="C6">
         <v>44659</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>45</v>
       </c>
@@ -473,8 +534,11 @@
       <c r="C7">
         <v>37030</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>55</v>
       </c>
@@ -484,8 +548,11 @@
       <c r="C8">
         <v>23961</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>65</v>
       </c>
@@ -495,8 +562,11 @@
       <c r="C9">
         <v>18136</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>75</v>
       </c>
@@ -506,8 +576,11 @@
       <c r="C10">
         <v>12315</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>85</v>
       </c>
@@ -516,6 +589,9 @@
       </c>
       <c r="C11">
         <v>4259</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
